--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -565,13 +565,7 @@
 ・Seriesの階層の(0008,0060)を集約する、または(0008,0060)　と　(0008, 0061) のOR。但し、重複する値は1つにまとめて表現。</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>「インスタンスにおける取得データの種類。」</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>.code</t>
@@ -873,6 +867,9 @@
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>コードは http://playbook.radlex.org/playbook/SearchRadlexAction に該当があれば使わなければならない。ただし、実施された行為のタイプにこれらのコードがなじまない場合は他のコードが利用される可能性がある。</t>
@@ -3343,13 +3340,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3385,13 +3380,13 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3399,10 +3394,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3425,16 +3420,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3484,7 +3479,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3499,16 +3494,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3516,10 +3511,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3542,16 +3537,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3601,7 +3596,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3616,16 +3611,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3633,14 +3628,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3659,16 +3654,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3682,7 +3677,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3718,7 +3713,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3733,16 +3728,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3750,10 +3745,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3776,19 +3771,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3837,7 +3832,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3852,16 +3847,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3869,14 +3864,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3895,16 +3890,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3954,7 +3949,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3972,13 +3967,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3986,14 +3981,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4012,16 +4007,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4071,7 +4066,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4089,13 +4084,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4103,10 +4098,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4129,19 +4124,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4190,7 +4185,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4208,7 +4203,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4222,14 +4217,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4248,16 +4243,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4307,7 +4302,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4325,10 +4320,10 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -4339,14 +4334,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4365,16 +4360,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4424,7 +4419,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4442,10 +4437,10 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4456,10 +4451,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4482,16 +4477,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4541,7 +4536,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4556,13 +4551,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4573,14 +4568,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4599,16 +4594,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4634,14 +4629,14 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4658,7 +4653,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4673,13 +4668,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4690,10 +4685,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4716,19 +4711,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4777,7 +4772,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4792,27 +4787,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4835,16 +4830,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4870,14 +4865,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4894,7 +4889,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4909,16 +4904,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4926,10 +4921,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4952,16 +4947,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5011,7 +5006,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5026,27 +5021,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5069,16 +5064,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5128,7 +5123,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5143,10 +5138,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5160,14 +5155,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5186,16 +5181,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5245,7 +5240,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5263,10 +5258,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5277,10 +5272,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5303,16 +5298,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5362,7 +5357,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5380,7 +5375,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5394,10 +5389,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5420,13 +5415,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5477,7 +5472,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5495,7 +5490,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5509,10 +5504,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5541,7 +5536,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5594,7 +5589,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5612,7 +5607,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5626,14 +5621,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5655,10 +5650,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5713,7 +5708,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5745,14 +5740,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5774,16 +5769,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5796,7 +5791,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5832,7 +5827,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5850,10 +5845,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5864,14 +5859,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5890,16 +5885,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5913,7 +5908,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5949,7 +5944,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5967,10 +5962,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5981,14 +5976,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6010,13 +6005,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6042,14 +6037,12 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6066,7 +6059,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6084,10 +6077,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6098,14 +6091,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6124,16 +6117,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6147,7 +6140,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6183,7 +6176,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6201,10 +6194,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6215,14 +6208,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6241,16 +6234,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6300,7 +6293,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6318,10 +6311,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6332,10 +6325,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6358,19 +6351,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6419,7 +6412,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6437,7 +6430,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6451,14 +6444,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6480,13 +6473,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6512,14 +6505,14 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6536,7 +6529,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6554,10 +6547,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6568,10 +6561,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6597,13 +6590,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6629,14 +6622,14 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6653,7 +6646,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6671,10 +6664,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6685,10 +6678,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6711,16 +6704,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6770,7 +6763,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6781,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6802,10 +6795,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6828,16 +6821,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6887,7 +6880,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6905,10 +6898,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6919,14 +6912,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6945,19 +6938,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7006,7 +6999,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7021,13 +7014,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7038,10 +7031,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7064,13 +7057,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7121,7 +7114,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7139,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7153,10 +7146,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7185,7 +7178,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7238,7 +7231,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7256,7 +7249,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7270,14 +7263,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7299,10 +7292,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7357,7 +7350,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7389,10 +7382,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7415,17 +7408,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7450,14 +7443,14 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7474,7 +7467,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7492,7 +7485,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7506,10 +7499,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7532,16 +7525,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7591,7 +7584,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7609,24 +7602,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7649,16 +7642,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7708,7 +7701,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7726,7 +7719,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7740,10 +7733,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7766,13 +7759,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7823,7 +7816,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7841,7 +7834,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7855,10 +7848,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7887,7 +7880,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7940,7 +7933,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7958,7 +7951,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7972,14 +7965,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8001,10 +7994,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8059,7 +8052,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8091,14 +8084,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8120,16 +8113,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8142,7 +8135,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8178,7 +8171,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8196,10 +8189,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8210,14 +8203,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8239,13 +8232,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8271,14 +8264,14 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8295,7 +8288,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8313,10 +8306,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8327,14 +8320,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8353,16 +8346,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8412,7 +8405,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8430,10 +8423,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8444,10 +8437,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8470,16 +8463,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8529,7 +8522,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8547,10 +8540,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -275,7 +275,7 @@
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -303,10 +303,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -319,10 +319,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -342,7 +342,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -358,10 +358,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -370,7 +370,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -390,10 +390,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -416,13 +416,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -445,7 +445,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>
@@ -464,7 +464,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -525,7 +525,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「ImagingStudyの状態。」</t>
+    <t>ImagingStudyの状態。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/imagingstudy-status|4.0.1</t>
@@ -1064,7 +1064,7 @@
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1077,11 +1077,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1344,7 +1344,7 @@
     <t>ImagingStudy.series.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」(Pafōmansu no shurui)</t>
+    <t>「パフォーマンスの種類」</t>
   </si>
   <si>
     <t>"俳優のシリーズへの参加のタイプを区別する。"</t>
@@ -1353,7 +1353,7 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>「パフォーマーの関与のタイプ」</t>
+    <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
@@ -1369,7 +1369,7 @@
     <t>"シリーズを演奏したのは誰ですか。" (Shirīzu o ensō shita no wa dare desu ka.)</t>
   </si>
   <si>
-    <t>「シリーズを行った人または物を示す。」</t>
+    <t>シリーズを行った人または物を示す。</t>
   </si>
   <si>
     <t>【JP Core仕様】組織または撮影者</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -1230,10 +1230,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -6507,11 +6504,9 @@
       <c r="X40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6547,10 +6542,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6561,10 +6556,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6590,13 +6585,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6625,11 +6620,11 @@
         <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6646,7 +6641,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6659,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6678,10 +6673,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6704,16 +6699,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6763,7 +6758,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6781,10 +6776,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6795,10 +6790,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6824,13 +6819,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6880,7 +6875,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6901,7 +6896,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6912,14 +6907,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6941,16 +6936,16 @@
         <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6999,7 +6994,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7014,13 +7009,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7031,10 +7026,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7146,10 +7141,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7263,10 +7258,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7382,10 +7377,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7411,14 +7406,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7446,11 +7441,11 @@
         <v>267</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7467,7 +7462,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7499,10 +7494,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7525,16 +7520,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7584,7 +7579,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7602,24 +7597,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7645,13 +7640,13 @@
         <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7701,7 +7696,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7719,7 +7714,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7733,10 +7728,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7848,10 +7843,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7965,10 +7960,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8084,14 +8079,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8113,16 +8108,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8135,7 +8130,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8171,7 +8166,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8192,7 +8187,7 @@
         <v>341</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8203,14 +8198,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8232,13 +8227,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8267,11 +8262,11 @@
         <v>267</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8288,7 +8283,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8306,10 +8301,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8320,14 +8315,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8349,13 +8344,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8405,7 +8400,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8423,10 +8418,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8437,10 +8432,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8466,13 +8461,13 @@
         <v>310</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8522,7 +8517,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8535,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -274,8 +274,8 @@
     <t>DICOM画像研究で生成されたコンテンツの表現。 研究には、共通の文脈で収集または生成されたサービスオブジェクトペアインスタンス（SOPインスタンス - 画像またはその他のデータ）のセットで構成される一連のシリーズが含まれます。 シリーズは1つのモダリティのみ（X線、CT、MR、超音波など）、研究には複数の異なるモダリティのシリーズが含まれる場合があります。</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -303,10 +303,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -319,10 +319,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -342,7 +342,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -361,7 +361,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -390,10 +390,10 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト要約</t>
-  </si>
-  <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「人間の解釈のためのリソースのテキスト要約」</t>
+  </si>
+  <si>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -419,10 +419,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -445,7 +445,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
+    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -455,16 +455,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -525,7 +525,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>ImagingStudyの状態。</t>
+    <t>「ImagingStudyの状態。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/imagingstudy-status|4.0.1</t>
@@ -1064,7 +1064,7 @@
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1077,11 +1077,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>認識されなくても無視できない拡張機能</t>
-  </si>
-  <si>
-    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
+    <t>「認識されなくても無視できない拡張機能」</t>
+  </si>
+  <si>
+    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1350,7 +1350,7 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>パフォーマーの関与のタイプ</t>
+    <t>「パフォーマーの関与のタイプ」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
@@ -1366,7 +1366,7 @@
     <t>"シリーズを演奏したのは誰ですか。" (Shirīzu o ensō shita no wa dare desu ka.)</t>
   </si>
   <si>
-    <t>シリーズを行った人または物を示す。</t>
+    <t>「シリーズを行った人または物を示す。」</t>
   </si>
   <si>
     <t>【JP Core仕様】組織または撮影者</t>
@@ -1469,7 +1469,7 @@
     <t>このシリーズにおけるこのインスタンスの番号</t>
   </si>
   <si>
-    <t>シリーズ内のインスタンスの数。 (Shirīzu-nai no insutansu no kazu.)</t>
+    <t>シリーズ内のインスタンスの数。</t>
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -274,8 +274,8 @@
     <t>DICOM画像研究で生成されたコンテンツの表現。 研究には、共通の文脈で収集または生成されたサービスオブジェクトペアインスタンス（SOPインスタンス - 画像またはその他のデータ）のセットで構成される一連のシリーズが含まれます。 シリーズは1つのモダリティのみ（X線、CT、MR、超音波など）、研究には複数の異なるモダリティのシリーズが含まれる場合があります。</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -303,10 +303,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -319,10 +319,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -342,7 +342,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -358,10 +358,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -370,7 +370,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -390,10 +390,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -416,13 +416,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -445,7 +445,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -455,16 +455,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -512,7 +512,7 @@
     <t>ImagingStudy.status</t>
   </si>
   <si>
-    <t>"登録済み | 利用可能 | 取消済み | エラーで入力 | 不明" (Tōrokuzumi | Riyō kanō | Torikeshi zumi | Erā de nyūryoku | Fumei)</t>
+    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明</t>
   </si>
   <si>
     <t>ImagingStudyの現在のステータス</t>
@@ -525,7 +525,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「ImagingStudyの状態。」</t>
+    <t>ImagingStudyの状態。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/imagingstudy-status|4.0.1</t>
@@ -1064,7 +1064,7 @@
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1077,11 +1077,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1187,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t>"シリーズ関連インスタンスの数" (Shirīzu kanren insutansu no kazu)</t>
+    <t>シリーズ関連インスタンスの数</t>
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
@@ -1341,16 +1341,16 @@
     <t>ImagingStudy.series.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」</t>
-  </si>
-  <si>
-    <t>"俳優のシリーズへの参加のタイプを区別する。"</t>
+    <t>パフォーマンスの種類</t>
+  </si>
+  <si>
+    <t>俳優のシリーズへの参加のタイプを区別する。</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>「パフォーマーの関与のタイプ」</t>
+    <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
@@ -1363,10 +1363,10 @@
 </t>
   </si>
   <si>
-    <t>"シリーズを演奏したのは誰ですか。" (Shirīzu o ensō shita no wa dare desu ka.)</t>
-  </si>
-  <si>
-    <t>「シリーズを行った人または物を示す。」</t>
+    <t>シリーズを演奏したのは誰ですか。</t>
+  </si>
+  <si>
+    <t>シリーズを行った人または物を示す。</t>
   </si>
   <si>
     <t>【JP Core仕様】組織または撮影者</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -867,9 +867,6 @@
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>コードは http://playbook.radlex.org/playbook/SearchRadlexAction に該当があれば使わなければならない。ただし、実施された行為のタイプにこれらのコードがなじまない場合は他のコードが利用される可能性がある。</t>
@@ -1350,6 +1347,9 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
@@ -1447,10 +1447,7 @@
     <t>【JP Core仕様】SOPクラスUID。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
-    <t>インスタンスのSOPクラス。</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part04/sect_B.5.html#table_B.5-1</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1845,7 +1842,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="133.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="87.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -4626,13 +4623,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4665,7 +4662,7 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>259</v>
@@ -4682,10 +4679,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4708,19 +4705,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4769,7 +4766,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4784,27 +4781,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4830,13 +4827,13 @@
         <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4862,14 +4859,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4886,7 +4883,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4901,16 +4898,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4918,10 +4915,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4944,16 +4941,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5003,7 +5000,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5018,27 +5015,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5061,16 +5058,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5120,7 +5117,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5135,10 +5132,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5152,14 +5149,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5178,16 +5175,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5237,7 +5234,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5255,10 +5252,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5269,10 +5266,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5295,16 +5292,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5354,7 +5351,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5372,7 +5369,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5386,10 +5383,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5412,13 +5409,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5469,7 +5466,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5487,7 +5484,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5501,10 +5498,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5533,7 +5530,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5586,7 +5583,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5604,7 +5601,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5618,14 +5615,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5647,10 +5644,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5705,7 +5702,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5737,14 +5734,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5766,16 +5763,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5788,7 +5785,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5824,7 +5821,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5842,10 +5839,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5856,14 +5853,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5885,13 +5882,13 @@
         <v>240</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5905,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5941,7 +5938,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5959,10 +5956,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5973,14 +5970,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6002,13 +5999,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6056,7 +6053,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6077,7 +6074,7 @@
         <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6088,14 +6085,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6114,16 +6111,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6137,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6173,7 +6170,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6191,10 +6188,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6205,14 +6202,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6234,13 +6231,13 @@
         <v>240</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>249</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6290,7 +6287,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6311,7 +6308,7 @@
         <v>251</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6322,10 +6319,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6351,16 +6348,16 @@
         <v>232</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6409,7 +6406,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6441,14 +6438,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6470,13 +6467,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6502,11 +6499,11 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6524,7 +6521,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6542,10 +6539,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6556,10 +6553,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6585,13 +6582,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6617,14 +6614,14 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>386</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6641,7 +6638,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6659,10 +6656,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6673,10 +6670,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6699,16 +6696,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6758,7 +6755,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6776,10 +6773,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6790,10 +6787,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6819,13 +6816,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6875,7 +6872,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6896,7 +6893,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6907,14 +6904,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6933,19 +6930,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6994,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7009,13 +7006,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7026,10 +7023,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7052,13 +7049,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7109,7 +7106,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7127,7 +7124,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7141,10 +7138,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7173,7 +7170,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7226,7 +7223,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7244,7 +7241,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7258,14 +7255,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7287,10 +7284,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7345,7 +7342,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7377,10 +7374,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7406,14 +7403,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7438,7 +7435,7 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>267</v>
+        <v>414</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>415</v>
@@ -7462,7 +7459,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7637,7 +7634,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>426</v>
@@ -7754,13 +7751,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7811,7 +7808,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7829,7 +7826,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7875,7 +7872,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7928,7 +7925,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7946,7 +7943,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7967,7 +7964,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7989,10 +7986,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8047,7 +8044,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8184,7 +8181,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>440</v>
@@ -8259,13 +8256,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="Y55" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Y55" s="2"/>
+      <c r="Z55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8301,10 +8296,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8315,14 +8310,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8344,13 +8339,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8400,7 +8395,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8418,10 +8413,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8432,10 +8427,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8458,16 +8453,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8517,7 +8512,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8535,10 +8530,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -1817,17 +1817,17 @@
   <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.81640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.81640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.13671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.13671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="220.078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1836,27 +1836,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="59.36328125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="133.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.15234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="50.890625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="114.3125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="114.25" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="104.890625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="97.94921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="89.92578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -1341,7 +1341,7 @@
     <t>パフォーマンスの種類</t>
   </si>
   <si>
-    <t>俳優のシリーズへの参加のタイプを区別する。</t>
+    <t>実施者・撮影者のシリーズへの参加のタイプを区別する。</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
@@ -1363,7 +1363,7 @@
 </t>
   </si>
   <si>
-    <t>シリーズを演奏したのは誰ですか。</t>
+    <t>シリーズを実施・撮影したのは誰ですか。</t>
   </si>
   <si>
     <t>シリーズを行った人または物を示す。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -1227,7 +1227,10 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -6501,9 +6504,11 @@
       <c r="X40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Y40" s="2"/>
+      <c r="Y40" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6539,10 +6544,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6553,10 +6558,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6582,13 +6587,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6617,10 +6622,10 @@
         <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6638,7 +6643,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6656,10 +6661,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6670,10 +6675,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6696,16 +6701,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6755,7 +6760,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6778,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6787,10 +6792,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6816,13 +6821,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6872,7 +6877,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6898,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6904,14 +6909,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6933,16 +6938,16 @@
         <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6991,7 +6996,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7006,13 +7011,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7023,10 +7028,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,10 +7143,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7255,10 +7260,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7403,14 +7408,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7435,13 +7440,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7459,7 +7464,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7491,10 +7496,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7517,16 +7522,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7576,7 +7581,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7594,24 +7599,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7637,13 +7642,13 @@
         <v>316</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7693,7 +7698,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7711,7 +7716,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7725,10 +7730,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7840,10 +7845,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7957,10 +7962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8076,14 +8081,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8105,16 +8110,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8127,7 +8132,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8163,7 +8168,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8184,7 +8189,7 @@
         <v>340</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8195,14 +8200,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8224,13 +8229,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8256,11 +8261,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8278,7 +8283,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8296,10 +8301,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8310,14 +8315,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8339,13 +8344,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8395,7 +8400,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8413,10 +8418,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8427,10 +8432,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8456,13 +8461,13 @@
         <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8512,7 +8517,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8535,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -673,7 +673,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -881,7 +881,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1264,7 +1264,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -3038,7 +3038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>179</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>349</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>418</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>434</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>442</v>
       </c>
@@ -8549,12 +8549,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO57">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -618,7 +618,7 @@
     <t>この画像検査が関連しているEncounterリソース</t>
   </si>
   <si>
-    <t>このImagingStudyが行われるヘルスケアイベント（患者とヘルスケアプロバイダの相互作用など）。</t>
+    <t>このImagingStudyが行われる診療イベント（患者と医療提供者の相互作用など）。</t>
   </si>
   <si>
     <t>これは通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、それでもそのEncounterのコンテキストに関連付けられている（例：入院前の検査）  
@@ -1014,8 +1014,7 @@
     <t>スタディのイメージングマネージャの説明。実施されたスタディ（コンポーネント）の機関生成の説明または分類。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-検査に関するフリーコメント。</t>
+    <t>検査に関するフリーコメント。</t>
   </si>
   <si>
     <t>.text</t>
@@ -1167,8 +1166,7 @@
     <t>シリーズの記述。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-シリーズごとにつけられるフリーコメント。</t>
+    <t>シリーズごとにつけられるフリーコメント。</t>
   </si>
   <si>
     <t>CT Surview 180</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -865,7 +865,7 @@
     <t>実施されたProcedureのタイプを表すコード。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
   </si>
   <si>
@@ -922,7 +922,7 @@
     <t>ImagingStudyが要求された理由を示す臨床状態の説明。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 JP Coreでは未使用</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -980,14 +980,14 @@
 </t>
   </si>
   <si>
-    <t>ユーザが定義したコメント</t>
+    <t>ユーザーが定義したコメント</t>
   </si>
   <si>
     <t>推奨されるDICOMマッピングによると、この要素はスタディの説明属性（0008,1030）から派生している。画像検査に関する観察または所見は、この要素に記述するのではなく、Observationのような別のリソースに記録する必要がある。</t>
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。  
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。  
 コメント（Annotation型による記述）</t>
   </si>
   <si>
@@ -1120,7 +1120,7 @@
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
-上記UIDとは別に、ユーザ（または装置）が自由に決められる番号。</t>
+上記UIDとは別に、ユーザー（または装置）が自由に決められる番号。</t>
   </si>
   <si>
     <t>3</t>
@@ -1273,7 +1273,7 @@
   </si>
   <si>
     <t>参照は、実在のFHIRリソースへの参照である必要があり、内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。  
-【JP Core仕様】UIDは別のtagが存在するので、ユーザ側で自由に付与していい番号と思われる。</t>
+【JP Core仕様】UIDは別のtagが存在するので、ユーザー側で自由に付与していい番号と思われる。</t>
   </si>
   <si>
     <t>Role[classCode=SPEC]</t>
@@ -1471,7 +1471,7 @@
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
-【JP Core仕様】ユーザ（または装置）が自由に決められる画像ごとの番号。DICOMタグマッピングにある値をそのまま設定。</t>
+【JP Core仕様】ユーザー（または装置）が自由に決められる画像ごとの番号。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP, source[classCode=OBSSER, moodCode=EVN]].sequenceNumber</t>
